--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487643_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487643_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>13.0314</v>
+        <v>10.9658</v>
       </c>
       <c r="E2" t="n">
-        <v>9.7133</v>
+        <v>7.893</v>
       </c>
       <c r="F2" t="n">
-        <v>3.318</v>
+        <v>3.0727</v>
       </c>
       <c r="G2" t="n">
         <v>7.9598</v>
@@ -610,13 +610,13 @@
         <v>4.0747</v>
       </c>
       <c r="S2" t="n">
-        <v>3.8506</v>
+        <v>1.785</v>
       </c>
       <c r="T2" t="n">
-        <v>3.5329</v>
+        <v>1.7126</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3177</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>-1.8836</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. BUHORSKYI</t>
+          <t>L. RODRIGUEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.0252</v>
+        <v>7.6644</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9492</v>
+        <v>5.962</v>
       </c>
       <c r="F3" t="n">
-        <v>2.076</v>
+        <v>1.7023</v>
       </c>
       <c r="G3" t="n">
-        <v>2.851</v>
+        <v>7.3445</v>
       </c>
       <c r="H3" t="n">
-        <v>2.479</v>
+        <v>3.4578</v>
       </c>
       <c r="I3" t="n">
-        <v>0.372</v>
+        <v>3.8867</v>
       </c>
       <c r="J3" t="n">
-        <v>2.1856</v>
+        <v>8.510400000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>2.0638</v>
+        <v>2.8218</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1218</v>
+        <v>5.6886</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6654</v>
+        <v>-1.1659</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4152</v>
+        <v>0.636</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2502</v>
+        <v>-1.8019</v>
       </c>
       <c r="P3" t="n">
-        <v>0.194</v>
+        <v>-2.1344</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9702</v>
+        <v>-6.7911</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1642</v>
+        <v>4.6568</v>
       </c>
       <c r="S3" t="n">
-        <v>2.6981</v>
+        <v>0.3842</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4517</v>
+        <v>0.9488</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2463</v>
+        <v>-0.5646</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2821</v>
+        <v>2.0701</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2821</v>
+        <v>3.294</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ SANCHEZ</t>
+          <t>D. BUHORSKYI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.5752</v>
+        <v>4.9941</v>
       </c>
       <c r="E4" t="n">
-        <v>4.1182</v>
+        <v>3.1089</v>
       </c>
       <c r="F4" t="n">
-        <v>1.457</v>
+        <v>1.8852</v>
       </c>
       <c r="G4" t="n">
-        <v>7.3445</v>
+        <v>2.851</v>
       </c>
       <c r="H4" t="n">
-        <v>3.4578</v>
+        <v>2.479</v>
       </c>
       <c r="I4" t="n">
-        <v>3.8867</v>
+        <v>0.372</v>
       </c>
       <c r="J4" t="n">
-        <v>8.510400000000001</v>
+        <v>2.1856</v>
       </c>
       <c r="K4" t="n">
-        <v>2.8218</v>
+        <v>2.0638</v>
       </c>
       <c r="L4" t="n">
-        <v>5.6886</v>
+        <v>0.1218</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1659</v>
+        <v>0.6654</v>
       </c>
       <c r="N4" t="n">
-        <v>0.636</v>
+        <v>0.4152</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.8019</v>
+        <v>0.2502</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.1344</v>
+        <v>0.194</v>
       </c>
       <c r="Q4" t="n">
-        <v>-6.7911</v>
+        <v>-0.9702</v>
       </c>
       <c r="R4" t="n">
-        <v>4.6568</v>
+        <v>1.1642</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.705</v>
+        <v>1.6669</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8951</v>
+        <v>1.6114</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8099</v>
+        <v>0.0556</v>
       </c>
       <c r="V4" t="n">
-        <v>2.0701</v>
+        <v>0.2821</v>
       </c>
       <c r="W4" t="n">
-        <v>3.294</v>
+        <v>0.2821</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5447</v>
+        <v>2.8933</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4339</v>
+        <v>3.3549</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1108</v>
+        <v>-0.4616</v>
       </c>
       <c r="G5" t="n">
         <v>-1.2301</v>
@@ -844,13 +844,13 @@
         <v>3.6866</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1449</v>
+        <v>0.4935</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5843</v>
+        <v>0.5052</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5606</v>
+        <v>-0.0117</v>
       </c>
       <c r="V5" t="n">
         <v>1.8836</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. BERMEJO FAJARDO</t>
+          <t>P. BARCALA BELTRAN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3507</v>
+        <v>0.2262</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0052</v>
+        <v>-0.2153</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3559</v>
+        <v>0.4415</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2452</v>
+        <v>-3.177</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2513</v>
+        <v>0.6797</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0061</v>
+        <v>-3.8567</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1639</v>
+        <v>-0.2871</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4737</v>
+        <v>1.5119</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6901</v>
+        <v>-1.799</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4091</v>
+        <v>-2.8898</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.725</v>
+        <v>-0.8321</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-2.0577</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.1642</v>
+        <v>0.5821</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.9403</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7761</v>
+        <v>2.5224</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7766</v>
+        <v>1.2674</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9354</v>
+        <v>1.1182</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1588</v>
+        <v>0.1492</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2821</v>
+        <v>1.5537</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8462</v>
+        <v>0.894</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5642</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4497</v>
+        <v>-0.304</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6867</v>
+        <v>-0.4865</v>
       </c>
       <c r="F7" t="n">
-        <v>0.237</v>
+        <v>0.1825</v>
       </c>
       <c r="G7" t="n">
         <v>-0.6432</v>
@@ -1000,13 +1000,13 @@
         <v>0.194</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0004</v>
+        <v>0.1452</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0606</v>
+        <v>0.1396</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0601</v>
+        <v>0.0056</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. BARCALA BELTRAN</t>
+          <t>P. VILLANUEVA LAZARO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6889999999999999</v>
+        <v>-0.6571</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8579</v>
+        <v>-0.8835</v>
       </c>
       <c r="F8" t="n">
-        <v>0.169</v>
+        <v>0.2264</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.177</v>
+        <v>2.1503</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6797</v>
+        <v>-0.1582</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.8567</v>
+        <v>2.3084</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2871</v>
+        <v>2.9314</v>
       </c>
       <c r="K8" t="n">
-        <v>1.5119</v>
+        <v>-0.8897</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.799</v>
+        <v>3.8211</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.8898</v>
+        <v>-0.7811</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8321</v>
+        <v>0.7316</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.0577</v>
+        <v>-1.5127</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5821</v>
+        <v>-2.1344</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9403</v>
+        <v>-5.821</v>
       </c>
       <c r="R8" t="n">
-        <v>2.5224</v>
+        <v>3.6866</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3522</v>
+        <v>-0.6253</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4755</v>
+        <v>-0.0163</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1233</v>
+        <v>-0.609</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5537</v>
+        <v>-0.0478</v>
       </c>
       <c r="W8" t="n">
-        <v>0.894</v>
+        <v>2.0223</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6597</v>
+        <v>-2.0701</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. BAILLO HERNÁNDEZ</t>
+          <t>F. BERMEJO FAJARDO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4612</v>
+        <v>-0.8363</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4641</v>
+        <v>0.4651</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9254</v>
+        <v>-1.3014</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7954</v>
+        <v>-0.2452</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.711</v>
+        <v>-0.2513</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0844</v>
+        <v>0.0061</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3419</v>
+        <v>1.1639</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3419</v>
+        <v>0.4737</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.6901</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.1374</v>
+        <v>-1.4091</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0529</v>
+        <v>-0.725</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0844</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>0.194</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R9" t="n">
-        <v>0.194</v>
+        <v>0.7761</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1402</v>
+        <v>0.291</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1222</v>
+        <v>0.3953</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0179</v>
+        <v>-0.1043</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.8462</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. CARABALLO ROPERO</t>
+          <t>B. BAILLO HERNÁNDEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5808</v>
+        <v>-1.1643</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2424</v>
+        <v>0.6248</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6616</v>
+        <v>-1.7891</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3738</v>
+        <v>-1.7954</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0593</v>
+        <v>-0.711</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.4331</v>
+        <v>-1.0844</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2117</v>
+        <v>0.3419</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0824</v>
+        <v>0.3419</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.2941</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1621</v>
+        <v>-2.1374</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0231</v>
+        <v>-1.0529</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.139</v>
+        <v>-1.0844</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7761</v>
+        <v>0.194</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0.194</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5691000000000001</v>
+        <v>0.4371</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0606</v>
+        <v>0.2829</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6297</v>
+        <v>0.1542</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. VILLANUEVA LAZARO</t>
+          <t>D. CARABALLO ROPERO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8755</v>
+        <v>-1.5987</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6658</v>
+        <v>-2.0422</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2097</v>
+        <v>0.4435</v>
       </c>
       <c r="G11" t="n">
-        <v>2.1503</v>
+        <v>-1.3738</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1582</v>
+        <v>0.0593</v>
       </c>
       <c r="I11" t="n">
-        <v>2.3084</v>
+        <v>-1.4331</v>
       </c>
       <c r="J11" t="n">
-        <v>2.9314</v>
+        <v>-1.2117</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.8897</v>
+        <v>0.0824</v>
       </c>
       <c r="L11" t="n">
-        <v>3.8211</v>
+        <v>-1.2941</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7811</v>
+        <v>-0.1621</v>
       </c>
       <c r="N11" t="n">
-        <v>0.7316</v>
+        <v>-0.0231</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.5127</v>
+        <v>-0.139</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.1344</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.821</v>
+        <v>-0.9702</v>
       </c>
       <c r="R11" t="n">
-        <v>3.6866</v>
+        <v>0.194</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.8436</v>
+        <v>0.5513</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7986</v>
+        <v>0.1396</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.045</v>
+        <v>0.4116</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.0478</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>2.0223</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.0701</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. PETIT</t>
+          <t>C. DIN PENDA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1453</v>
+        <v>-1.7108</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7797</v>
+        <v>-2.617</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6344</v>
+        <v>0.9062</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.4125</v>
+        <v>-0.6338</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.5777</v>
+        <v>-1.1971</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8348</v>
+        <v>0.5633</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.6536</v>
+        <v>-1.0263</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.1081</v>
+        <v>-1.0669</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5455</v>
+        <v>0.0406</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7588</v>
+        <v>0.3925</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4696</v>
+        <v>-0.1302</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2892</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>0.3881</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q12" t="n">
         <v>-1.9403</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3284</v>
+        <v>0.7761</v>
       </c>
       <c r="S12" t="n">
-        <v>0.491</v>
+        <v>0.0872</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8142</v>
+        <v>0.3496</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3232</v>
+        <v>-0.2624</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6119</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.6119</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C. DIN PENDA</t>
+          <t>D. PETIT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.6355</v>
+        <v>-2.2727</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.3783</v>
+        <v>-2.8798</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7427</v>
+        <v>0.6071</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.6338</v>
+        <v>-2.4125</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.1971</v>
+        <v>-1.5777</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5633</v>
+        <v>-0.8348</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.0263</v>
+        <v>-1.6536</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.0669</v>
+        <v>-1.1081</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0406</v>
+        <v>-0.5455</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3925</v>
+        <v>-0.7588</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1302</v>
+        <v>-0.4696</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5227000000000001</v>
+        <v>-0.2892</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.1642</v>
+        <v>0.3881</v>
       </c>
       <c r="Q13" t="n">
         <v>-1.9403</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7761</v>
+        <v>2.3284</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8376</v>
+        <v>0.3637</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4116</v>
+        <v>0.7141</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4259</v>
+        <v>-0.3505</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-0.6119</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="14">
@@ -1501,22 +1501,22 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>16.9888</v>
+        <v>18.1999</v>
       </c>
       <c r="E14" t="n">
-        <v>11.0731</v>
+        <v>12.2844</v>
       </c>
       <c r="F14" t="n">
-        <v>5.915500000000001</v>
+        <v>5.915300000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>8.794599999999999</v>
+        <v>8.794600000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>8.905999999999999</v>
+        <v>8.906000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1115000000000012</v>
+        <v>-0.1115000000000003</v>
       </c>
       <c r="J14" t="n">
         <v>19.9167</v>
@@ -1543,16 +1543,16 @@
         <v>-25.2242</v>
       </c>
       <c r="R14" t="n">
-        <v>24.25389999999999</v>
+        <v>24.2539</v>
       </c>
       <c r="S14" t="n">
-        <v>5.636099999999999</v>
+        <v>6.8472</v>
       </c>
       <c r="T14" t="n">
-        <v>6.6897</v>
+        <v>7.901</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.0538</v>
+        <v>-1.0539</v>
       </c>
       <c r="V14" t="n">
         <v>3.5283</v>
@@ -1561,7 +1561,7 @@
         <v>9.690799999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.162600000000001</v>
+        <v>-6.1626</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.0902</v>
+        <v>9.6739</v>
       </c>
       <c r="E15" t="n">
-        <v>7.5826</v>
+        <v>8.984</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4924</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G15" t="n">
         <v>7.5422</v>
@@ -1624,13 +1624,13 @@
         <v>5.0448</v>
       </c>
       <c r="S15" t="n">
-        <v>-3.5893</v>
+        <v>-1.0055</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.6577</v>
+        <v>-0.2564</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.9315</v>
+        <v>-0.7492</v>
       </c>
       <c r="V15" t="n">
         <v>3.7194</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.1172</v>
+        <v>2.3225</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0718</v>
+        <v>1.7705</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0454</v>
+        <v>0.552</v>
       </c>
       <c r="G16" t="n">
         <v>-0.5264</v>
@@ -1702,13 +1702,13 @@
         <v>4.0747</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0137</v>
+        <v>0.219</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6778</v>
+        <v>0.3765</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6641</v>
+        <v>-0.1575</v>
       </c>
       <c r="V16" t="n">
         <v>1.2716</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1329</v>
+        <v>1.0539</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4758</v>
+        <v>-0.8762</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6087</v>
+        <v>1.9301</v>
       </c>
       <c r="G17" t="n">
         <v>0.0288</v>
@@ -1780,13 +1780,13 @@
         <v>2.1344</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1339</v>
+        <v>0.055</v>
       </c>
       <c r="T17" t="n">
-        <v>0.766</v>
+        <v>0.3656</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6321</v>
+        <v>-0.3107</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5847</v>
+        <v>-2.1031</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4251</v>
+        <v>-1.1258</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1596</v>
+        <v>-0.9772999999999999</v>
       </c>
       <c r="G18" t="n">
         <v>-0.7379</v>
@@ -1858,13 +1858,13 @@
         <v>2.5224</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2129</v>
+        <v>0.6945</v>
       </c>
       <c r="T18" t="n">
-        <v>1.5545</v>
+        <v>0.8538</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3416</v>
+        <v>-0.1592</v>
       </c>
       <c r="V18" t="n">
         <v>-2.4477</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. LOBATO ANDRADE</t>
+          <t>A. GOMEZ SERRANO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1324</v>
+        <v>-2.2038</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4664</v>
+        <v>-0.9655</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.666</v>
+        <v>-1.2383</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.6415</v>
+        <v>-1.3763</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8758</v>
+        <v>-0.407</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7658</v>
+        <v>-0.9693000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6061</v>
+        <v>0.618</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0206</v>
+        <v>-0.1812</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6267</v>
+        <v>0.7992</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0354</v>
+        <v>-1.9943</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8964</v>
+        <v>-0.2258</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.139</v>
+        <v>-1.7685</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.7761</v>
+        <v>0.5821</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1642</v>
+        <v>-1.3582</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3881</v>
+        <v>1.9403</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2853</v>
+        <v>-1.1275</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3039</v>
+        <v>-0.2252</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0186</v>
+        <v>-0.9023</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. BLANCO-ARGIBAY GONZALEZ</t>
+          <t>J. LOBATO ANDRADE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.154</v>
+        <v>-2.2808</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2421</v>
+        <v>-1.6666</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0881</v>
+        <v>-0.6143</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.023</v>
+        <v>-1.6415</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.3851</v>
+        <v>-0.8758</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6379</v>
+        <v>-0.7658</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.9558</v>
+        <v>-0.6061</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.141</v>
+        <v>0.0206</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1852</v>
+        <v>-0.6267</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.0672</v>
+        <v>-1.0354</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2441</v>
+        <v>-0.8964</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-0.139</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1642</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1344</v>
+        <v>-1.1642</v>
       </c>
       <c r="R20" t="n">
-        <v>3.2985</v>
+        <v>0.3881</v>
       </c>
       <c r="S20" t="n">
-        <v>1.5406</v>
+        <v>0.1368</v>
       </c>
       <c r="T20" t="n">
-        <v>1.5556</v>
+        <v>0.1037</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.015</v>
+        <v>0.0331</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.8358</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.7075</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.1283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. GOMEZ SERRANO</t>
+          <t>I. BLANCO-ARGIBAY GONZALEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.2165</v>
+        <v>-2.8815</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.466</v>
+        <v>-3.0429</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7505</v>
+        <v>0.1614</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.3763</v>
+        <v>-3.023</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.407</v>
+        <v>-2.3851</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9693000000000001</v>
+        <v>-0.6379</v>
       </c>
       <c r="J21" t="n">
-        <v>0.618</v>
+        <v>-0.9558</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1812</v>
+        <v>-1.141</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7992</v>
+        <v>0.1852</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.9943</v>
+        <v>-2.0672</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2258</v>
+        <v>-1.2441</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.7685</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5821</v>
+        <v>1.1642</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.3582</v>
+        <v>-2.1344</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9403</v>
+        <v>3.2985</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.1402</v>
+        <v>0.8131</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7257</v>
+        <v>0.7548</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.4145</v>
+        <v>0.0584</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2821</v>
+        <v>-1.8358</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.7075</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2821</v>
+        <v>-1.1283</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.2243</v>
+        <v>-3.7332</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.438</v>
+        <v>-2.5381</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7863</v>
+        <v>-1.1951</v>
       </c>
       <c r="G22" t="n">
         <v>-0.7624</v>
@@ -2170,13 +2170,13 @@
         <v>2.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9394</v>
+        <v>-0.4484</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1795</v>
+        <v>-0.2796</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7599</v>
+        <v>-0.1688</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.4723</v>
+        <v>-5.4191</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.4061</v>
+        <v>-2.5052</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.0662</v>
+        <v>-2.9139</v>
       </c>
       <c r="G23" t="n">
         <v>-3.0507</v>
@@ -2248,13 +2248,13 @@
         <v>2.1344</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4679</v>
+        <v>-0.4147</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.5142</v>
+        <v>-0.6133</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0462</v>
+        <v>0.1985</v>
       </c>
       <c r="V23" t="n">
         <v>-2.7298</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.5449</v>
+        <v>-7.4137</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.6505</v>
+        <v>-3.9498</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.8944</v>
+        <v>-3.4639</v>
       </c>
       <c r="G24" t="n">
         <v>-5.2474</v>
@@ -2326,13 +2326,13 @@
         <v>0.7761</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.6855</v>
+        <v>-0.5543</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7268</v>
+        <v>-0.0261</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.9587</v>
+        <v>-0.5282</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2239</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-16.9888</v>
+        <v>-12.9849</v>
       </c>
       <c r="E25" t="n">
         <v>-5.9156</v>
       </c>
       <c r="F25" t="n">
-        <v>-11.0732</v>
+        <v>-7.0693</v>
       </c>
       <c r="G25" t="n">
         <v>-8.794599999999999</v>
@@ -2395,7 +2395,7 @@
         <v>-9.5932</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9701999999999996</v>
+        <v>0.9701999999999994</v>
       </c>
       <c r="Q25" t="n">
         <v>-24.254</v>
@@ -2404,13 +2404,13 @@
         <v>25.2242</v>
       </c>
       <c r="S25" t="n">
-        <v>-5.6359</v>
+        <v>-1.632</v>
       </c>
       <c r="T25" t="n">
-        <v>1.0539</v>
+        <v>1.0538</v>
       </c>
       <c r="U25" t="n">
-        <v>-6.689800000000001</v>
+        <v>-2.6859</v>
       </c>
       <c r="V25" t="n">
         <v>-3.528300000000001</v>
